--- a/307 шт. - для парсера_result.xlsx
+++ b/307 шт. - для парсера_result.xlsx
@@ -487,46 +487,14 @@
           <t>https://old.bankrot.fedresurs.ru/PrivatePersonCard.aspx?ID=26CEAA742DEB1BEA6C54AB429674EFB4</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16.02.2026</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>О признании гражданина банкротом и введении реализации имущества гражданина</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>А33-20590/2025</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Степанова Елена Владимировна</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>109028, г.Москва, а/я7</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12.02.2026</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>660013, г.Красноярск, ул. Энергетиков, д. 34, кв. 108</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>не завершено</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
